--- a/z0bug_odoo/data/account_rc_type.xlsx
+++ b/z0bug_odoo/data/account_rc_type.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">payment_journal_id</t>
   </si>
   <si>
-    <t xml:space="preserve">transitory_account_id</t>
+    <t xml:space="preserve">transient_account_id</t>
   </si>
   <si>
     <t xml:space="preserve">l10n_it_reverse_charge.account_rc_type_1</t>

--- a/z0bug_odoo/data/account_rc_type.xlsx
+++ b/z0bug_odoo/data/account_rc_type.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -55,10 +55,13 @@
     <t xml:space="preserve">transient_account_id</t>
   </si>
   <si>
+    <t xml:space="preserve">fiscal_document_type_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">l10n_it_reverse_charge.account_rc_type_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Reverse charge locale</t>
+    <t xml:space="preserve">Reverse charge locale (deprecated)</t>
   </si>
   <si>
     <t xml:space="preserve">Usare per RC locale (italia)</t>
@@ -82,10 +85,13 @@
     <t xml:space="preserve">external.490050</t>
   </si>
   <si>
+    <t xml:space="preserve">external.TD19</t>
+  </si>
+  <si>
     <t xml:space="preserve">l10n_it_reverse_charge.account_rc_type_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Reverse charge Extra-EU</t>
+    <t xml:space="preserve">Reverse charge Extra-EU  (deprecated)</t>
   </si>
   <si>
     <t xml:space="preserve">Usare per RC estero no EU</t>
@@ -94,13 +100,19 @@
     <t xml:space="preserve">other</t>
   </si>
   <si>
+    <t xml:space="preserve">external.TD17</t>
+  </si>
+  <si>
     <t xml:space="preserve">l10n_it_reverse_charge.account_rc_type_3</t>
   </si>
   <si>
-    <t xml:space="preserve">Reverse charge EU</t>
+    <t xml:space="preserve">Reverse charge EU (deprecated)</t>
   </si>
   <si>
     <t xml:space="preserve">Usare per RC interna EU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">external.TD18</t>
   </si>
 </sst>
 </file>
@@ -110,7 +122,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -133,9 +145,15 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10.5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -187,11 +205,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -318,19 +336,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="11.78515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.3"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="11.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="23.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="23.41"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1015" min="13" style="1" width="11.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1016" style="1" width="11.52"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1025" style="1" width="11.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -367,101 +389,113 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
